--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O558"/>
+  <dimension ref="A1:O559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33794,6 +33794,65 @@
       </c>
       <c r="N558" s="32" t="inlineStr"/>
       <c r="O558" s="31" t="inlineStr"/>
+    </row>
+    <row r="559" ht="16" customHeight="1">
+      <c r="A559" s="33" t="inlineStr">
+        <is>
+          <t>7d25d84d0c39</t>
+        </is>
+      </c>
+      <c r="B559" s="33" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="C559" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D559" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E559" s="33" t="inlineStr">
+        <is>
+          <t>Newcastle Upon Tyne, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F559" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G559" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H559" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I559" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J559" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K559" s="35" t="inlineStr"/>
+      <c r="L559" s="35" t="inlineStr"/>
+      <c r="M559" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N559" s="36" t="inlineStr"/>
+      <c r="O559" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34097,6 +34156,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J556" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J558" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J559" r:id="rId290"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O559"/>
+  <dimension ref="A1:O561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33853,6 +33853,124 @@
       </c>
       <c r="N559" s="36" t="inlineStr"/>
       <c r="O559" s="35" t="inlineStr"/>
+    </row>
+    <row r="560" ht="16" customHeight="1">
+      <c r="A560" s="28" t="inlineStr">
+        <is>
+          <t>95d8bc905a17</t>
+        </is>
+      </c>
+      <c r="B560" s="28" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="C560" s="28" t="inlineStr">
+        <is>
+          <t>Senior/ Civil Engineer (Water Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D560" s="28" t="inlineStr">
+        <is>
+          <t>Sweco</t>
+        </is>
+      </c>
+      <c r="E560" s="28" t="inlineStr">
+        <is>
+          <t>Edinburgh, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F560" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G560" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H560" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I560" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J560" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K560" s="31" t="inlineStr"/>
+      <c r="L560" s="31" t="inlineStr"/>
+      <c r="M560" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N560" s="32" t="inlineStr"/>
+      <c r="O560" s="31" t="inlineStr"/>
+    </row>
+    <row r="561" ht="16" customHeight="1">
+      <c r="A561" s="33" t="inlineStr">
+        <is>
+          <t>3e8d51197793</t>
+        </is>
+      </c>
+      <c r="B561" s="33" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="C561" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D561" s="33" t="inlineStr">
+        <is>
+          <t>CHG Electrical</t>
+        </is>
+      </c>
+      <c r="E561" s="33" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F561" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G561" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H561" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I561" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J561" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K561" s="35" t="inlineStr"/>
+      <c r="L561" s="35" t="inlineStr"/>
+      <c r="M561" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N561" s="36" t="inlineStr"/>
+      <c r="O561" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34157,6 +34275,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J558" r:id="rId289"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J559" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J560" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J561" r:id="rId292"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O561"/>
+  <dimension ref="A1:O562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33971,6 +33971,65 @@
       </c>
       <c r="N561" s="36" t="inlineStr"/>
       <c r="O561" s="35" t="inlineStr"/>
+    </row>
+    <row r="562" ht="16" customHeight="1">
+      <c r="A562" s="28" t="inlineStr">
+        <is>
+          <t>0ba3d06a8d55</t>
+        </is>
+      </c>
+      <c r="B562" s="28" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="C562" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D562" s="28" t="inlineStr">
+        <is>
+          <t>CHG Electrical</t>
+        </is>
+      </c>
+      <c r="E562" s="28" t="inlineStr">
+        <is>
+          <t>Rotherham, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F562" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G562" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H562" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I562" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J562" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K562" s="31" t="inlineStr"/>
+      <c r="L562" s="31" t="inlineStr"/>
+      <c r="M562" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N562" s="32" t="inlineStr"/>
+      <c r="O562" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34277,6 +34336,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J559" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J560" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J561" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J562" r:id="rId293"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O562"/>
+  <dimension ref="A1:O563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34030,6 +34030,65 @@
       </c>
       <c r="N562" s="32" t="inlineStr"/>
       <c r="O562" s="31" t="inlineStr"/>
+    </row>
+    <row r="563" ht="16" customHeight="1">
+      <c r="A563" s="33" t="inlineStr">
+        <is>
+          <t>3afffc56b8d2</t>
+        </is>
+      </c>
+      <c r="B563" s="33" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="C563" s="33" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water</t>
+        </is>
+      </c>
+      <c r="D563" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E563" s="33" t="inlineStr">
+        <is>
+          <t>Reading, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F563" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G563" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H563" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I563" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J563" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K563" s="35" t="inlineStr"/>
+      <c r="L563" s="35" t="inlineStr"/>
+      <c r="M563" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N563" s="36" t="inlineStr"/>
+      <c r="O563" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34337,6 +34396,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J560" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J561" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J562" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J563" r:id="rId294"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O563"/>
+  <dimension ref="A1:O566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34089,6 +34089,183 @@
       </c>
       <c r="N563" s="36" t="inlineStr"/>
       <c r="O563" s="35" t="inlineStr"/>
+    </row>
+    <row r="564" ht="16" customHeight="1">
+      <c r="A564" s="28" t="inlineStr">
+        <is>
+          <t>f72e2cb8c8f2</t>
+        </is>
+      </c>
+      <c r="B564" s="28" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="C564" s="28" t="inlineStr">
+        <is>
+          <t>Clean Water (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D564" s="28" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E564" s="28" t="inlineStr">
+        <is>
+          <t>Edinburgh, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F564" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G564" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H564" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I564" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J564" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K564" s="31" t="inlineStr"/>
+      <c r="L564" s="31" t="inlineStr"/>
+      <c r="M564" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N564" s="32" t="inlineStr"/>
+      <c r="O564" s="31" t="inlineStr"/>
+    </row>
+    <row r="565" ht="16" customHeight="1">
+      <c r="A565" s="33" t="inlineStr">
+        <is>
+          <t>a7547f28e3ab</t>
+        </is>
+      </c>
+      <c r="B565" s="33" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="C565" s="33" t="inlineStr">
+        <is>
+          <t>Expression of Interest - Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D565" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E565" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F565" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G565" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H565" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I565" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J565" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K565" s="35" t="inlineStr"/>
+      <c r="L565" s="35" t="inlineStr"/>
+      <c r="M565" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N565" s="36" t="inlineStr"/>
+      <c r="O565" s="35" t="inlineStr"/>
+    </row>
+    <row r="566" ht="16" customHeight="1">
+      <c r="A566" s="28" t="inlineStr">
+        <is>
+          <t>2f9d7ede476f</t>
+        </is>
+      </c>
+      <c r="B566" s="28" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="C566" s="28" t="inlineStr">
+        <is>
+          <t>Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D566" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E566" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F566" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G566" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H566" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I566" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J566" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K566" s="31" t="inlineStr"/>
+      <c r="L566" s="31" t="inlineStr"/>
+      <c r="M566" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N566" s="32" t="inlineStr"/>
+      <c r="O566" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34397,6 +34574,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J561" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J562" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J563" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J564" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J565" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J566" r:id="rId297"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O566"/>
+  <dimension ref="A1:O568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34266,6 +34266,124 @@
       </c>
       <c r="N566" s="32" t="inlineStr"/>
       <c r="O566" s="31" t="inlineStr"/>
+    </row>
+    <row r="567" ht="16" customHeight="1">
+      <c r="A567" s="33" t="inlineStr">
+        <is>
+          <t>8938595e08b1</t>
+        </is>
+      </c>
+      <c r="B567" s="33" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="C567" s="33" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D567" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E567" s="33" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F567" s="33" t="inlineStr">
+        <is>
+          <t>£48,192 – £48,192</t>
+        </is>
+      </c>
+      <c r="G567" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H567" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I567" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J567" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K567" s="35" t="inlineStr"/>
+      <c r="L567" s="35" t="inlineStr"/>
+      <c r="M567" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N567" s="36" t="inlineStr"/>
+      <c r="O567" s="35" t="inlineStr"/>
+    </row>
+    <row r="568" ht="16" customHeight="1">
+      <c r="A568" s="28" t="inlineStr">
+        <is>
+          <t>5d6c10a9e7ce</t>
+        </is>
+      </c>
+      <c r="B568" s="28" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="C568" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer – Water &amp; Infrastructure Projects – 20324</t>
+        </is>
+      </c>
+      <c r="D568" s="28" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E568" s="28" t="inlineStr">
+        <is>
+          <t>Barnsley, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F568" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G568" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H568" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I568" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J568" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K568" s="31" t="inlineStr"/>
+      <c r="L568" s="31" t="inlineStr"/>
+      <c r="M568" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N568" s="32" t="inlineStr"/>
+      <c r="O568" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34577,6 +34695,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J564" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J565" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J566" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J567" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId299"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O568"/>
+  <dimension ref="A1:O569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34384,6 +34384,65 @@
       </c>
       <c r="N568" s="32" t="inlineStr"/>
       <c r="O568" s="31" t="inlineStr"/>
+    </row>
+    <row r="569" ht="16" customHeight="1">
+      <c r="A569" s="33" t="inlineStr">
+        <is>
+          <t>7ad2f144267e</t>
+        </is>
+      </c>
+      <c r="B569" s="33" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="C569" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D569" s="33" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E569" s="33" t="inlineStr">
+        <is>
+          <t>Edinburgh, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F569" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G569" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H569" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I569" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J569" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K569" s="35" t="inlineStr"/>
+      <c r="L569" s="35" t="inlineStr"/>
+      <c r="M569" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N569" s="36" t="inlineStr"/>
+      <c r="O569" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34697,6 +34756,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J566" r:id="rId297"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J567" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId300"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O569"/>
+  <dimension ref="A1:O570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34443,6 +34443,65 @@
       </c>
       <c r="N569" s="36" t="inlineStr"/>
       <c r="O569" s="35" t="inlineStr"/>
+    </row>
+    <row r="570" ht="16" customHeight="1">
+      <c r="A570" s="28" t="inlineStr">
+        <is>
+          <t>6426b26b3403</t>
+        </is>
+      </c>
+      <c r="B570" s="28" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C570" s="28" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D570" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E570" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F570" s="28" t="inlineStr">
+        <is>
+          <t>£49,307 – £49,307</t>
+        </is>
+      </c>
+      <c r="G570" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H570" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I570" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J570" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K570" s="31" t="inlineStr"/>
+      <c r="L570" s="31" t="inlineStr"/>
+      <c r="M570" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N570" s="32" t="inlineStr"/>
+      <c r="O570" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34757,6 +34816,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J567" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId299"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId301"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O570"/>
+  <dimension ref="A1:O571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34502,6 +34502,65 @@
       </c>
       <c r="N570" s="32" t="inlineStr"/>
       <c r="O570" s="31" t="inlineStr"/>
+    </row>
+    <row r="571" ht="16" customHeight="1">
+      <c r="A571" s="33" t="inlineStr">
+        <is>
+          <t>cbdf9f965fdd</t>
+        </is>
+      </c>
+      <c r="B571" s="33" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="C571" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D571" s="33" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E571" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F571" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G571" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H571" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I571" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J571" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K571" s="35" t="inlineStr"/>
+      <c r="L571" s="35" t="inlineStr"/>
+      <c r="M571" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N571" s="36" t="inlineStr"/>
+      <c r="O571" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34817,6 +34876,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId299"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId302"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O571"/>
+  <dimension ref="A1:O572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34561,6 +34561,65 @@
       </c>
       <c r="N571" s="36" t="inlineStr"/>
       <c r="O571" s="35" t="inlineStr"/>
+    </row>
+    <row r="572" ht="16" customHeight="1">
+      <c r="A572" s="28" t="inlineStr">
+        <is>
+          <t>751da83c012f</t>
+        </is>
+      </c>
+      <c r="B572" s="28" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C572" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Design Engineer (Projects / Deck Equipment)</t>
+        </is>
+      </c>
+      <c r="D572" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E572" s="28" t="inlineStr">
+        <is>
+          <t>Aberdeen, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F572" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G572" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H572" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I572" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J572" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K572" s="31" t="inlineStr"/>
+      <c r="L572" s="31" t="inlineStr"/>
+      <c r="M572" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N572" s="32" t="inlineStr"/>
+      <c r="O572" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34877,6 +34936,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId303"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O572"/>
+  <dimension ref="A1:O574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34620,6 +34620,124 @@
       </c>
       <c r="N572" s="32" t="inlineStr"/>
       <c r="O572" s="31" t="inlineStr"/>
+    </row>
+    <row r="573" ht="16" customHeight="1">
+      <c r="A573" s="33" t="inlineStr">
+        <is>
+          <t>0fc6fff59ac2</t>
+        </is>
+      </c>
+      <c r="B573" s="33" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C573" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Design Engineer (Projects / Deck Equipment)</t>
+        </is>
+      </c>
+      <c r="D573" s="33" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E573" s="33" t="inlineStr">
+        <is>
+          <t>Aberdeen, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F573" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G573" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H573" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I573" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J573" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K573" s="35" t="inlineStr"/>
+      <c r="L573" s="35" t="inlineStr"/>
+      <c r="M573" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N573" s="36" t="inlineStr"/>
+      <c r="O573" s="35" t="inlineStr"/>
+    </row>
+    <row r="574" ht="16" customHeight="1">
+      <c r="A574" s="28" t="inlineStr">
+        <is>
+          <t>a07023a53071</t>
+        </is>
+      </c>
+      <c r="B574" s="28" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C574" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D574" s="28" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E574" s="28" t="inlineStr">
+        <is>
+          <t>Exeter, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F574" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G574" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H574" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I574" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="J574" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K574" s="31" t="inlineStr"/>
+      <c r="L574" s="31" t="inlineStr"/>
+      <c r="M574" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N574" s="32" t="inlineStr"/>
+      <c r="O574" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34937,6 +35055,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J573" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId305"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O574"/>
+  <dimension ref="A1:O576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34738,6 +34738,124 @@
       </c>
       <c r="N574" s="32" t="inlineStr"/>
       <c r="O574" s="31" t="inlineStr"/>
+    </row>
+    <row r="575" ht="16" customHeight="1">
+      <c r="A575" s="33" t="inlineStr">
+        <is>
+          <t>b93d7af2225c</t>
+        </is>
+      </c>
+      <c r="B575" s="33" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="C575" s="33" t="inlineStr">
+        <is>
+          <t>Clean Water Network Engineer</t>
+        </is>
+      </c>
+      <c r="D575" s="33" t="inlineStr">
+        <is>
+          <t>Celnor Group</t>
+        </is>
+      </c>
+      <c r="E575" s="33" t="inlineStr">
+        <is>
+          <t>West Malling, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F575" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G575" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H575" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I575" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="J575" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K575" s="35" t="inlineStr"/>
+      <c r="L575" s="35" t="inlineStr"/>
+      <c r="M575" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N575" s="36" t="inlineStr"/>
+      <c r="O575" s="35" t="inlineStr"/>
+    </row>
+    <row r="576" ht="16" customHeight="1">
+      <c r="A576" s="28" t="inlineStr">
+        <is>
+          <t>d71be2956d69</t>
+        </is>
+      </c>
+      <c r="B576" s="28" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="C576" s="28" t="inlineStr">
+        <is>
+          <t>Water Network Analyst</t>
+        </is>
+      </c>
+      <c r="D576" s="28" t="inlineStr">
+        <is>
+          <t>NWG (Northumbrian Water Group)</t>
+        </is>
+      </c>
+      <c r="E576" s="28" t="inlineStr">
+        <is>
+          <t>Washington, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F576" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G576" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H576" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I576" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J576" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K576" s="31" t="inlineStr"/>
+      <c r="L576" s="31" t="inlineStr"/>
+      <c r="M576" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N576" s="32" t="inlineStr"/>
+      <c r="O576" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35057,6 +35175,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId303"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J573" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J575" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J576" r:id="rId307"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O576"/>
+  <dimension ref="A1:O579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -34856,6 +34856,183 @@
       </c>
       <c r="N576" s="32" t="inlineStr"/>
       <c r="O576" s="31" t="inlineStr"/>
+    </row>
+    <row r="577" ht="16" customHeight="1">
+      <c r="A577" s="33" t="inlineStr">
+        <is>
+          <t>5dd252d786c1</t>
+        </is>
+      </c>
+      <c r="B577" s="33" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="C577" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller -  Modeller to Associate</t>
+        </is>
+      </c>
+      <c r="D577" s="33" t="inlineStr">
+        <is>
+          <t>Talent Link</t>
+        </is>
+      </c>
+      <c r="E577" s="33" t="inlineStr">
+        <is>
+          <t>Greater London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F577" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G577" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H577" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I577" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J577" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K577" s="35" t="inlineStr"/>
+      <c r="L577" s="35" t="inlineStr"/>
+      <c r="M577" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N577" s="36" t="inlineStr"/>
+      <c r="O577" s="35" t="inlineStr"/>
+    </row>
+    <row r="578" ht="16" customHeight="1">
+      <c r="A578" s="28" t="inlineStr">
+        <is>
+          <t>7a80eec850a6</t>
+        </is>
+      </c>
+      <c r="B578" s="28" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="C578" s="28" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D578" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E578" s="28" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F578" s="28" t="inlineStr">
+        <is>
+          <t>£48,192 – £48,192</t>
+        </is>
+      </c>
+      <c r="G578" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H578" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I578" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J578" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K578" s="31" t="inlineStr"/>
+      <c r="L578" s="31" t="inlineStr"/>
+      <c r="M578" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N578" s="32" t="inlineStr"/>
+      <c r="O578" s="31" t="inlineStr"/>
+    </row>
+    <row r="579" ht="16" customHeight="1">
+      <c r="A579" s="33" t="inlineStr">
+        <is>
+          <t>245a325b8ce6</t>
+        </is>
+      </c>
+      <c r="B579" s="33" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="C579" s="33" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D579" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E579" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F579" s="33" t="inlineStr">
+        <is>
+          <t>£49,307 – £49,307</t>
+        </is>
+      </c>
+      <c r="G579" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H579" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I579" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J579" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K579" s="35" t="inlineStr"/>
+      <c r="L579" s="35" t="inlineStr"/>
+      <c r="M579" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N579" s="36" t="inlineStr"/>
+      <c r="O579" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35177,6 +35354,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId305"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J575" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J576" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J577" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId310"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O579"/>
+  <dimension ref="A1:O580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35033,6 +35033,65 @@
       </c>
       <c r="N579" s="36" t="inlineStr"/>
       <c r="O579" s="35" t="inlineStr"/>
+    </row>
+    <row r="580" ht="16" customHeight="1">
+      <c r="A580" s="28" t="inlineStr">
+        <is>
+          <t>e92adf6cc855</t>
+        </is>
+      </c>
+      <c r="B580" s="28" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="C580" s="28" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D580" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E580" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F580" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G580" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H580" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I580" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J580" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K580" s="31" t="inlineStr"/>
+      <c r="L580" s="31" t="inlineStr"/>
+      <c r="M580" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N580" s="32" t="inlineStr"/>
+      <c r="O580" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35357,6 +35416,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J577" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId309"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId311"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O580"/>
+  <dimension ref="A1:O582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35092,6 +35092,124 @@
       </c>
       <c r="N580" s="32" t="inlineStr"/>
       <c r="O580" s="31" t="inlineStr"/>
+    </row>
+    <row r="581" ht="16" customHeight="1">
+      <c r="A581" s="33" t="inlineStr">
+        <is>
+          <t>71f7b0a4cf0b</t>
+        </is>
+      </c>
+      <c r="B581" s="33" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C581" s="33" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D581" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E581" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F581" s="33" t="inlineStr">
+        <is>
+          <t>£49,301 – £49,301</t>
+        </is>
+      </c>
+      <c r="G581" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H581" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I581" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J581" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K581" s="35" t="inlineStr"/>
+      <c r="L581" s="35" t="inlineStr"/>
+      <c r="M581" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N581" s="36" t="inlineStr"/>
+      <c r="O581" s="35" t="inlineStr"/>
+    </row>
+    <row r="582" ht="16" customHeight="1">
+      <c r="A582" s="28" t="inlineStr">
+        <is>
+          <t>4171f80346b7</t>
+        </is>
+      </c>
+      <c r="B582" s="28" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C582" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic/Flood Modeller</t>
+        </is>
+      </c>
+      <c r="D582" s="28" t="inlineStr">
+        <is>
+          <t>TipTopJob</t>
+        </is>
+      </c>
+      <c r="E582" s="28" t="inlineStr">
+        <is>
+          <t>Stockton-On-Tees, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F582" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G582" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H582" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I582" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J582" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K582" s="31" t="inlineStr"/>
+      <c r="L582" s="31" t="inlineStr"/>
+      <c r="M582" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N582" s="32" t="inlineStr"/>
+      <c r="O582" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35417,6 +35535,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId309"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J581" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J582" r:id="rId313"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O582"/>
+  <dimension ref="A1:O585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35210,6 +35210,183 @@
       </c>
       <c r="N582" s="32" t="inlineStr"/>
       <c r="O582" s="31" t="inlineStr"/>
+    </row>
+    <row r="583" ht="16" customHeight="1">
+      <c r="A583" s="33" t="inlineStr">
+        <is>
+          <t>a60cf78b2a22</t>
+        </is>
+      </c>
+      <c r="B583" s="33" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C583" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Manager</t>
+        </is>
+      </c>
+      <c r="D583" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E583" s="33" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F583" s="33" t="inlineStr">
+        <is>
+          <t>£43,559 – £43,559</t>
+        </is>
+      </c>
+      <c r="G583" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H583" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I583" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J583" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K583" s="35" t="inlineStr"/>
+      <c r="L583" s="35" t="inlineStr"/>
+      <c r="M583" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N583" s="36" t="inlineStr"/>
+      <c r="O583" s="35" t="inlineStr"/>
+    </row>
+    <row r="584" ht="16" customHeight="1">
+      <c r="A584" s="28" t="inlineStr">
+        <is>
+          <t>33dce3ff7049</t>
+        </is>
+      </c>
+      <c r="B584" s="28" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C584" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Manager</t>
+        </is>
+      </c>
+      <c r="D584" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E584" s="28" t="inlineStr">
+        <is>
+          <t>Aldgate, Central London</t>
+        </is>
+      </c>
+      <c r="F584" s="28" t="inlineStr">
+        <is>
+          <t>£46,135 – £46,135</t>
+        </is>
+      </c>
+      <c r="G584" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H584" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I584" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J584" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K584" s="31" t="inlineStr"/>
+      <c r="L584" s="31" t="inlineStr"/>
+      <c r="M584" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N584" s="32" t="inlineStr"/>
+      <c r="O584" s="31" t="inlineStr"/>
+    </row>
+    <row r="585" ht="16" customHeight="1">
+      <c r="A585" s="33" t="inlineStr">
+        <is>
+          <t>672f4bf26070</t>
+        </is>
+      </c>
+      <c r="B585" s="33" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C585" s="33" t="inlineStr">
+        <is>
+          <t>Senior/ Civil Engineer (Water Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D585" s="33" t="inlineStr">
+        <is>
+          <t>Sweco</t>
+        </is>
+      </c>
+      <c r="E585" s="33" t="inlineStr">
+        <is>
+          <t>Glasgow, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F585" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G585" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H585" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I585" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J585" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K585" s="35" t="inlineStr"/>
+      <c r="L585" s="35" t="inlineStr"/>
+      <c r="M585" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N585" s="36" t="inlineStr"/>
+      <c r="O585" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35537,6 +35714,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId311"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J581" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J582" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J583" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J584" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J585" r:id="rId316"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O585"/>
+  <dimension ref="A1:O587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35387,6 +35387,124 @@
       </c>
       <c r="N585" s="36" t="inlineStr"/>
       <c r="O585" s="35" t="inlineStr"/>
+    </row>
+    <row r="586" ht="16" customHeight="1">
+      <c r="A586" s="28" t="inlineStr">
+        <is>
+          <t>46a9d88a64ac</t>
+        </is>
+      </c>
+      <c r="B586" s="28" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C586" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Manager</t>
+        </is>
+      </c>
+      <c r="D586" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E586" s="28" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F586" s="28" t="inlineStr">
+        <is>
+          <t>£42,270 – £42,270</t>
+        </is>
+      </c>
+      <c r="G586" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H586" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I586" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J586" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K586" s="31" t="inlineStr"/>
+      <c r="L586" s="31" t="inlineStr"/>
+      <c r="M586" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N586" s="32" t="inlineStr"/>
+      <c r="O586" s="31" t="inlineStr"/>
+    </row>
+    <row r="587" ht="16" customHeight="1">
+      <c r="A587" s="33" t="inlineStr">
+        <is>
+          <t>d1e61463bb62</t>
+        </is>
+      </c>
+      <c r="B587" s="33" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C587" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Manager</t>
+        </is>
+      </c>
+      <c r="D587" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E587" s="33" t="inlineStr">
+        <is>
+          <t>Aldgate, Central London</t>
+        </is>
+      </c>
+      <c r="F587" s="33" t="inlineStr">
+        <is>
+          <t>£44,293 – £44,293</t>
+        </is>
+      </c>
+      <c r="G587" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H587" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I587" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J587" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K587" s="35" t="inlineStr"/>
+      <c r="L587" s="35" t="inlineStr"/>
+      <c r="M587" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N587" s="36" t="inlineStr"/>
+      <c r="O587" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35717,6 +35835,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J583" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J584" r:id="rId315"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J585" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J586" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J587" r:id="rId318"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O587"/>
+  <dimension ref="A1:O588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35505,6 +35505,65 @@
       </c>
       <c r="N587" s="36" t="inlineStr"/>
       <c r="O587" s="35" t="inlineStr"/>
+    </row>
+    <row r="588" ht="16" customHeight="1">
+      <c r="A588" s="28" t="inlineStr">
+        <is>
+          <t>7a5a97fbfc5b</t>
+        </is>
+      </c>
+      <c r="B588" s="28" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="C588" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D588" s="28" t="inlineStr">
+        <is>
+          <t>CHG Electrical</t>
+        </is>
+      </c>
+      <c r="E588" s="28" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F588" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G588" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H588" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I588" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J588" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K588" s="31" t="inlineStr"/>
+      <c r="L588" s="31" t="inlineStr"/>
+      <c r="M588" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N588" s="32" t="inlineStr"/>
+      <c r="O588" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35837,6 +35896,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J585" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J586" r:id="rId317"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J587" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J588" r:id="rId319"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O588"/>
+  <dimension ref="A1:O589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35564,6 +35564,65 @@
       </c>
       <c r="N588" s="32" t="inlineStr"/>
       <c r="O588" s="31" t="inlineStr"/>
+    </row>
+    <row r="589" ht="16" customHeight="1">
+      <c r="A589" s="33" t="inlineStr">
+        <is>
+          <t>d1aa58424c51</t>
+        </is>
+      </c>
+      <c r="B589" s="33" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C589" s="33" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D589" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E589" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F589" s="33" t="inlineStr">
+        <is>
+          <t>£49,301 – £49,301</t>
+        </is>
+      </c>
+      <c r="G589" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H589" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I589" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J589" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K589" s="35" t="inlineStr"/>
+      <c r="L589" s="35" t="inlineStr"/>
+      <c r="M589" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N589" s="36" t="inlineStr"/>
+      <c r="O589" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35897,6 +35956,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J586" r:id="rId317"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J587" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J588" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J589" r:id="rId320"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O589"/>
+  <dimension ref="A1:O590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35623,6 +35623,65 @@
       </c>
       <c r="N589" s="36" t="inlineStr"/>
       <c r="O589" s="35" t="inlineStr"/>
+    </row>
+    <row r="590" ht="16" customHeight="1">
+      <c r="A590" s="28" t="inlineStr">
+        <is>
+          <t>63d5d0501e95</t>
+        </is>
+      </c>
+      <c r="B590" s="28" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="C590" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller- Part time or Full time</t>
+        </is>
+      </c>
+      <c r="D590" s="28" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E590" s="28" t="inlineStr">
+        <is>
+          <t>Haultwick, Ware</t>
+        </is>
+      </c>
+      <c r="F590" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G590" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H590" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I590" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="J590" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K590" s="31" t="inlineStr"/>
+      <c r="L590" s="31" t="inlineStr"/>
+      <c r="M590" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N590" s="32" t="inlineStr"/>
+      <c r="O590" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -35957,6 +36016,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J587" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J588" r:id="rId319"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J589" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J590" r:id="rId321"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O590"/>
+  <dimension ref="A1:O591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35682,6 +35682,65 @@
       </c>
       <c r="N590" s="32" t="inlineStr"/>
       <c r="O590" s="31" t="inlineStr"/>
+    </row>
+    <row r="591" ht="16" customHeight="1">
+      <c r="A591" s="33" t="inlineStr">
+        <is>
+          <t>b165a1666d90</t>
+        </is>
+      </c>
+      <c r="B591" s="33" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="C591" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller- Part time or Full time</t>
+        </is>
+      </c>
+      <c r="D591" s="33" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E591" s="33" t="inlineStr">
+        <is>
+          <t>Stanstead Abbotts, Ware</t>
+        </is>
+      </c>
+      <c r="F591" s="33" t="inlineStr">
+        <is>
+          <t>£36,577 – £36,577</t>
+        </is>
+      </c>
+      <c r="G591" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H591" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I591" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="J591" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K591" s="35" t="inlineStr"/>
+      <c r="L591" s="35" t="inlineStr"/>
+      <c r="M591" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N591" s="36" t="inlineStr"/>
+      <c r="O591" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36017,6 +36076,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J588" r:id="rId319"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J589" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J590" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J591" r:id="rId322"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O591"/>
+  <dimension ref="A1:O594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35741,6 +35741,183 @@
       </c>
       <c r="N591" s="36" t="inlineStr"/>
       <c r="O591" s="35" t="inlineStr"/>
+    </row>
+    <row r="592" ht="16" customHeight="1">
+      <c r="A592" s="28" t="inlineStr">
+        <is>
+          <t>1a0c656d755b</t>
+        </is>
+      </c>
+      <c r="B592" s="28" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="C592" s="28" t="inlineStr">
+        <is>
+          <t>Drainage and Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D592" s="28" t="inlineStr">
+        <is>
+          <t>Kier Group</t>
+        </is>
+      </c>
+      <c r="E592" s="28" t="inlineStr">
+        <is>
+          <t>Exeter, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F592" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G592" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H592" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I592" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J592" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K592" s="31" t="inlineStr"/>
+      <c r="L592" s="31" t="inlineStr"/>
+      <c r="M592" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N592" s="32" t="inlineStr"/>
+      <c r="O592" s="31" t="inlineStr"/>
+    </row>
+    <row r="593" ht="16" customHeight="1">
+      <c r="A593" s="33" t="inlineStr">
+        <is>
+          <t>ed0df068bf0f</t>
+        </is>
+      </c>
+      <c r="B593" s="33" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="C593" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D593" s="33" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E593" s="33" t="inlineStr">
+        <is>
+          <t>Chalvey, Slough</t>
+        </is>
+      </c>
+      <c r="F593" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G593" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H593" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I593" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J593" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K593" s="35" t="inlineStr"/>
+      <c r="L593" s="35" t="inlineStr"/>
+      <c r="M593" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N593" s="36" t="inlineStr"/>
+      <c r="O593" s="35" t="inlineStr"/>
+    </row>
+    <row r="594" ht="16" customHeight="1">
+      <c r="A594" s="28" t="inlineStr">
+        <is>
+          <t>64f61b102050</t>
+        </is>
+      </c>
+      <c r="B594" s="28" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="C594" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D594" s="28" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E594" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F594" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G594" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H594" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I594" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J594" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K594" s="31" t="inlineStr"/>
+      <c r="L594" s="31" t="inlineStr"/>
+      <c r="M594" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N594" s="32" t="inlineStr"/>
+      <c r="O594" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36077,6 +36254,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J589" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J590" r:id="rId321"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J591" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J592" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J593" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J594" r:id="rId325"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O594"/>
+  <dimension ref="A1:O595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35918,6 +35918,65 @@
       </c>
       <c r="N594" s="32" t="inlineStr"/>
       <c r="O594" s="31" t="inlineStr"/>
+    </row>
+    <row r="595" ht="16" customHeight="1">
+      <c r="A595" s="33" t="inlineStr">
+        <is>
+          <t>641e4dd29478</t>
+        </is>
+      </c>
+      <c r="B595" s="33" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="C595" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D595" s="33" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E595" s="33" t="inlineStr">
+        <is>
+          <t>Edinburgh, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F595" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G595" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H595" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I595" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J595" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K595" s="35" t="inlineStr"/>
+      <c r="L595" s="35" t="inlineStr"/>
+      <c r="M595" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N595" s="36" t="inlineStr"/>
+      <c r="O595" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36257,6 +36316,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J592" r:id="rId323"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J593" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J594" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J595" r:id="rId326"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O595"/>
+  <dimension ref="A1:O596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -35977,6 +35977,65 @@
       </c>
       <c r="N595" s="36" t="inlineStr"/>
       <c r="O595" s="35" t="inlineStr"/>
+    </row>
+    <row r="596" ht="16" customHeight="1">
+      <c r="A596" s="28" t="inlineStr">
+        <is>
+          <t>a860d535e95e</t>
+        </is>
+      </c>
+      <c r="B596" s="28" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="C596" s="28" t="inlineStr">
+        <is>
+          <t>Expression of Interest - Drainage and Water Design</t>
+        </is>
+      </c>
+      <c r="D596" s="28" t="inlineStr">
+        <is>
+          <t>Kier Group</t>
+        </is>
+      </c>
+      <c r="E596" s="28" t="inlineStr">
+        <is>
+          <t>England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F596" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G596" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H596" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I596" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J596" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K596" s="31" t="inlineStr"/>
+      <c r="L596" s="31" t="inlineStr"/>
+      <c r="M596" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N596" s="32" t="inlineStr"/>
+      <c r="O596" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36317,6 +36376,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J593" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J594" r:id="rId325"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J595" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J596" r:id="rId327"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O596"/>
+  <dimension ref="A1:O597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36036,6 +36036,65 @@
       </c>
       <c r="N596" s="32" t="inlineStr"/>
       <c r="O596" s="31" t="inlineStr"/>
+    </row>
+    <row r="597" ht="16" customHeight="1">
+      <c r="A597" s="33" t="inlineStr">
+        <is>
+          <t>5a6139a09231</t>
+        </is>
+      </c>
+      <c r="B597" s="33" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="C597" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D597" s="33" t="inlineStr">
+        <is>
+          <t>CHG Electrical</t>
+        </is>
+      </c>
+      <c r="E597" s="33" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F597" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G597" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H597" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I597" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J597" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K597" s="35" t="inlineStr"/>
+      <c r="L597" s="35" t="inlineStr"/>
+      <c r="M597" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N597" s="36" t="inlineStr"/>
+      <c r="O597" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36377,6 +36436,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J594" r:id="rId325"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J595" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J596" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J597" r:id="rId328"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O597"/>
+  <dimension ref="A1:O598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36095,6 +36095,65 @@
       </c>
       <c r="N597" s="36" t="inlineStr"/>
       <c r="O597" s="35" t="inlineStr"/>
+    </row>
+    <row r="598" ht="16" customHeight="1">
+      <c r="A598" s="28" t="inlineStr">
+        <is>
+          <t>6539bc0652b9</t>
+        </is>
+      </c>
+      <c r="B598" s="28" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C598" s="28" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D598" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E598" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F598" s="28" t="inlineStr">
+        <is>
+          <t>£49,301 – £49,301</t>
+        </is>
+      </c>
+      <c r="G598" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H598" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I598" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J598" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K598" s="31" t="inlineStr"/>
+      <c r="L598" s="31" t="inlineStr"/>
+      <c r="M598" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N598" s="32" t="inlineStr"/>
+      <c r="O598" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36437,6 +36496,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J595" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J596" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J597" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J598" r:id="rId329"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O598"/>
+  <dimension ref="A1:O599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36154,6 +36154,65 @@
       </c>
       <c r="N598" s="32" t="inlineStr"/>
       <c r="O598" s="31" t="inlineStr"/>
+    </row>
+    <row r="599" ht="16" customHeight="1">
+      <c r="A599" s="33" t="inlineStr">
+        <is>
+          <t>0c5213574a46</t>
+        </is>
+      </c>
+      <c r="B599" s="33" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="C599" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D599" s="33" t="inlineStr">
+        <is>
+          <t>CHG Electrical</t>
+        </is>
+      </c>
+      <c r="E599" s="33" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F599" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G599" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H599" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I599" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J599" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K599" s="35" t="inlineStr"/>
+      <c r="L599" s="35" t="inlineStr"/>
+      <c r="M599" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N599" s="36" t="inlineStr"/>
+      <c r="O599" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36497,6 +36556,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J596" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J597" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J598" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J599" r:id="rId330"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O599"/>
+  <dimension ref="A1:O600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36213,6 +36213,65 @@
       </c>
       <c r="N599" s="36" t="inlineStr"/>
       <c r="O599" s="35" t="inlineStr"/>
+    </row>
+    <row r="600" ht="16" customHeight="1">
+      <c r="A600" s="28" t="inlineStr">
+        <is>
+          <t>85a9fc1d9c4f</t>
+        </is>
+      </c>
+      <c r="B600" s="28" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="C600" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Wastewater AMP8</t>
+        </is>
+      </c>
+      <c r="D600" s="28" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E600" s="28" t="inlineStr">
+        <is>
+          <t>Plymouth, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F600" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G600" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H600" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I600" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="J600" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K600" s="31" t="inlineStr"/>
+      <c r="L600" s="31" t="inlineStr"/>
+      <c r="M600" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N600" s="32" t="inlineStr"/>
+      <c r="O600" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36557,6 +36616,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J597" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J598" r:id="rId329"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J599" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J600" r:id="rId331"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O600"/>
+  <dimension ref="A1:O601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36272,6 +36272,65 @@
       </c>
       <c r="N600" s="32" t="inlineStr"/>
       <c r="O600" s="31" t="inlineStr"/>
+    </row>
+    <row r="601" ht="16" customHeight="1">
+      <c r="A601" s="33" t="inlineStr">
+        <is>
+          <t>71d0270028a2</t>
+        </is>
+      </c>
+      <c r="B601" s="33" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="C601" s="33" t="inlineStr">
+        <is>
+          <t>Major Water Infrastructure Programme PMO Manager</t>
+        </is>
+      </c>
+      <c r="D601" s="33" t="inlineStr">
+        <is>
+          <t>Ofwat</t>
+        </is>
+      </c>
+      <c r="E601" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F601" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G601" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H601" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I601" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J601" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K601" s="35" t="inlineStr"/>
+      <c r="L601" s="35" t="inlineStr"/>
+      <c r="M601" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N601" s="36" t="inlineStr"/>
+      <c r="O601" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36617,6 +36676,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J598" r:id="rId329"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J599" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J600" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J601" r:id="rId332"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O601"/>
+  <dimension ref="A1:O602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36331,6 +36331,65 @@
       </c>
       <c r="N601" s="36" t="inlineStr"/>
       <c r="O601" s="35" t="inlineStr"/>
+    </row>
+    <row r="602" ht="16" customHeight="1">
+      <c r="A602" s="28" t="inlineStr">
+        <is>
+          <t>ec053e939e8d</t>
+        </is>
+      </c>
+      <c r="B602" s="28" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="C602" s="28" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water (Design &amp; Build)</t>
+        </is>
+      </c>
+      <c r="D602" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E602" s="28" t="inlineStr">
+        <is>
+          <t>Newcastle Upon Tyne, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F602" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G602" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H602" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I602" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J602" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K602" s="31" t="inlineStr"/>
+      <c r="L602" s="31" t="inlineStr"/>
+      <c r="M602" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N602" s="32" t="inlineStr"/>
+      <c r="O602" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36677,6 +36736,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J599" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J600" r:id="rId331"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J601" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J602" r:id="rId333"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O602"/>
+  <dimension ref="A1:O605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36390,6 +36390,183 @@
       </c>
       <c r="N602" s="32" t="inlineStr"/>
       <c r="O602" s="31" t="inlineStr"/>
+    </row>
+    <row r="603" ht="16" customHeight="1">
+      <c r="A603" s="33" t="inlineStr">
+        <is>
+          <t>c391744ba56c</t>
+        </is>
+      </c>
+      <c r="B603" s="33" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="C603" s="33" t="inlineStr">
+        <is>
+          <t>Hydrologist- Flood Risk and Hydraulic Modelling Consultant</t>
+        </is>
+      </c>
+      <c r="D603" s="33" t="inlineStr">
+        <is>
+          <t>Ramboll</t>
+        </is>
+      </c>
+      <c r="E603" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F603" s="33" t="inlineStr">
+        <is>
+          <t>£43,813 – £43,813</t>
+        </is>
+      </c>
+      <c r="G603" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H603" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I603" s="33" t="n">
+        <v>110</v>
+      </c>
+      <c r="J603" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K603" s="35" t="inlineStr"/>
+      <c r="L603" s="35" t="inlineStr"/>
+      <c r="M603" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N603" s="36" t="inlineStr"/>
+      <c r="O603" s="35" t="inlineStr"/>
+    </row>
+    <row r="604" ht="16" customHeight="1">
+      <c r="A604" s="28" t="inlineStr">
+        <is>
+          <t>0342f2bdec3c</t>
+        </is>
+      </c>
+      <c r="B604" s="28" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="C604" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Manager (SuDS)</t>
+        </is>
+      </c>
+      <c r="D604" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E604" s="28" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F604" s="28" t="inlineStr">
+        <is>
+          <t>£42,027 – £42,027</t>
+        </is>
+      </c>
+      <c r="G604" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H604" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I604" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J604" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K604" s="31" t="inlineStr"/>
+      <c r="L604" s="31" t="inlineStr"/>
+      <c r="M604" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N604" s="32" t="inlineStr"/>
+      <c r="O604" s="31" t="inlineStr"/>
+    </row>
+    <row r="605" ht="16" customHeight="1">
+      <c r="A605" s="33" t="inlineStr">
+        <is>
+          <t>7a1beaebfb92</t>
+        </is>
+      </c>
+      <c r="B605" s="33" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="C605" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Manager (SuDS)</t>
+        </is>
+      </c>
+      <c r="D605" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E605" s="33" t="inlineStr">
+        <is>
+          <t>Aldgate, Central London</t>
+        </is>
+      </c>
+      <c r="F605" s="33" t="inlineStr">
+        <is>
+          <t>£44,512 – £44,512</t>
+        </is>
+      </c>
+      <c r="G605" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H605" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I605" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J605" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K605" s="35" t="inlineStr"/>
+      <c r="L605" s="35" t="inlineStr"/>
+      <c r="M605" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N605" s="36" t="inlineStr"/>
+      <c r="O605" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36737,6 +36914,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J600" r:id="rId331"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J601" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J602" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J603" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J604" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J605" r:id="rId336"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O605"/>
+  <dimension ref="A1:O607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -36567,6 +36567,124 @@
       </c>
       <c r="N605" s="36" t="inlineStr"/>
       <c r="O605" s="35" t="inlineStr"/>
+    </row>
+    <row r="606" ht="16" customHeight="1">
+      <c r="A606" s="28" t="inlineStr">
+        <is>
+          <t>ba80cdc2635e</t>
+        </is>
+      </c>
+      <c r="B606" s="28" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="C606" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Manager (SuDS)</t>
+        </is>
+      </c>
+      <c r="D606" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E606" s="28" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F606" s="28" t="inlineStr">
+        <is>
+          <t>£40,784 – £40,784</t>
+        </is>
+      </c>
+      <c r="G606" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H606" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I606" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J606" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K606" s="31" t="inlineStr"/>
+      <c r="L606" s="31" t="inlineStr"/>
+      <c r="M606" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N606" s="32" t="inlineStr"/>
+      <c r="O606" s="31" t="inlineStr"/>
+    </row>
+    <row r="607" ht="16" customHeight="1">
+      <c r="A607" s="33" t="inlineStr">
+        <is>
+          <t>75ea99160060</t>
+        </is>
+      </c>
+      <c r="B607" s="33" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="C607" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Manager (SuDS)</t>
+        </is>
+      </c>
+      <c r="D607" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E607" s="33" t="inlineStr">
+        <is>
+          <t>Aldgate, Central London</t>
+        </is>
+      </c>
+      <c r="F607" s="33" t="inlineStr">
+        <is>
+          <t>£42,735 – £42,735</t>
+        </is>
+      </c>
+      <c r="G607" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H607" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I607" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J607" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K607" s="35" t="inlineStr"/>
+      <c r="L607" s="35" t="inlineStr"/>
+      <c r="M607" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N607" s="36" t="inlineStr"/>
+      <c r="O607" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -36917,6 +37035,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J603" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J604" r:id="rId335"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J605" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J606" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J607" r:id="rId338"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
